--- a/NBFC-MF/Borrowers/Thongam_Deme_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Thongam_Deme_Daily.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Date</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t>Thongam_Deme</t>
-  </si>
-  <si>
-    <t>11se</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1186,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>18900</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1223,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>16348.408466459945</v>
+        <v>14758.991922004241</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1260,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3651.591533540055</v>
+        <v>5241.0080779957589</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1338,8 +1335,8 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>24</v>
+      <c r="A18" s="2">
+        <v>46276</v>
       </c>
       <c r="B18" s="23">
         <f t="shared" si="3"/>
@@ -1368,201 +1365,215 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A19" s="19">
+        <v>46278</v>
+      </c>
+      <c r="B19" s="24">
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="21" t="str">
+      <c r="D19" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E19" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H19" s="21" t="str">
+        <v>76.091311734233543</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="5"/>
+        <v>223.90868826576644</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="4"/>
+        <v>16124.499778194178</v>
+      </c>
+      <c r="H19" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3875.5002218058216</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A20" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B20" s="23">
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
+      <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E20" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
+        <v>75.049161005385074</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="5"/>
+        <v>224.95083899461491</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="4"/>
+        <v>15899.548939199563</v>
+      </c>
+      <c r="H20" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4100.4510608004366</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46280</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
+      <c r="D21" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E21" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
+        <v>74.002159736121882</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>225.99784026387812</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>15673.551098935684</v>
+      </c>
+      <c r="H21" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4326.4489010643156</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A22" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B22" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
+      <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E22" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
+        <v>72.95028535030248</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="5"/>
+        <v>227.04971464969753</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="4"/>
+        <v>15446.501384285986</v>
+      </c>
+      <c r="H22" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4553.4986157140138</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A23" s="19">
+        <v>46285</v>
+      </c>
+      <c r="B23" s="24">
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="C23" s="20"/>
-      <c r="D23" s="21" t="str">
+      <c r="D23" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E23" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F23" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G23" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H23" s="21" t="str">
+        <v>71.893515166707971</v>
+      </c>
+      <c r="F23" s="21">
+        <f t="shared" si="5"/>
+        <v>228.10648483329203</v>
+      </c>
+      <c r="G23" s="21">
+        <f t="shared" si="4"/>
+        <v>15218.394899452695</v>
+      </c>
+      <c r="H23" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4781.6051005473055</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A24" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B24" s="23">
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="4" t="str">
+      <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E24" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E24" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="str">
+        <v>70.831826398552991</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="5"/>
+        <v>229.16817360144699</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="4"/>
+        <v>14989.226725851247</v>
+      </c>
+      <c r="H24" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5010.7732741487525</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A25" s="19">
+        <v>46285</v>
+      </c>
+      <c r="B25" s="24">
+        <f t="shared" si="3"/>
+        <v>24</v>
       </c>
       <c r="C25" s="20"/>
-      <c r="D25" s="21" t="str">
+      <c r="D25" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E25" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G25" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H25" s="21" t="str">
+        <v>69.765196152994378</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="5"/>
+        <v>230.23480384700562</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="4"/>
+        <v>14758.991922004241</v>
+      </c>
+      <c r="H25" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5241.0080779957589</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Thongam_Deme_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Thongam_Deme_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>16800</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>14758.991922004241</v>
+        <v>12154.574982735843</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>5241.0080779957589</v>
+        <v>7845.4250172641568</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1577,311 +1577,333 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A26" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B26" s="23">
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E26" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E26" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G26" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="str">
+        <v>68.693601430637528</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="5"/>
+        <v>231.30639856936247</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="4"/>
+        <v>14527.685523434879</v>
+      </c>
+      <c r="H26" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5472.3144765651214</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A27" s="19">
+        <v>46290</v>
+      </c>
+      <c r="B27" s="24">
+        <f t="shared" si="3"/>
+        <v>26</v>
       </c>
       <c r="C27" s="20"/>
-      <c r="D27" s="21" t="str">
+      <c r="D27" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E27" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G27" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H27" s="21" t="str">
+        <v>67.617019125040443</v>
+      </c>
+      <c r="F27" s="21">
+        <f t="shared" si="5"/>
+        <v>232.38298087495957</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="4"/>
+        <v>14295.302542559919</v>
+      </c>
+      <c r="H27" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5704.6974574400811</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A28" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B28" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="4" t="str">
+      <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E28" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="str">
+        <v>66.53542602221556</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="5"/>
+        <v>233.46457397778443</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="4"/>
+        <v>14061.837968582135</v>
+      </c>
+      <c r="H28" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5938.1620314178654</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A29" s="19">
+        <v>46290</v>
+      </c>
+      <c r="B29" s="24">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="21" t="str">
+      <c r="D29" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E29" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E29" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G29" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H29" s="21" t="str">
+        <v>65.44879880012914</v>
+      </c>
+      <c r="F29" s="21">
+        <f t="shared" si="5"/>
+        <v>234.55120119987086</v>
+      </c>
+      <c r="G29" s="21">
+        <f t="shared" si="4"/>
+        <v>13827.286767382264</v>
+      </c>
+      <c r="H29" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6172.7132326177361</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A30" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B30" s="23">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="4" t="str">
+      <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E30" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E30" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="str">
+        <v>64.357114028198367</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="5"/>
+        <v>235.64288597180163</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>13591.643881410462</v>
+      </c>
+      <c r="H30" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6408.3561185895378</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A31" s="19">
+        <v>46291</v>
+      </c>
+      <c r="B31" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="C31" s="20"/>
-      <c r="D31" s="21" t="str">
+      <c r="D31" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E31" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E31" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F31" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H31" s="21" t="str">
+        <v>63.260348166786208</v>
+      </c>
+      <c r="F31" s="21">
+        <f t="shared" si="5"/>
+        <v>236.7396518332138</v>
+      </c>
+      <c r="G31" s="21">
+        <f t="shared" si="4"/>
+        <v>13354.904229577249</v>
+      </c>
+      <c r="H31" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6645.0957704227512</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A32" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B32" s="23">
+        <f t="shared" si="3"/>
+        <v>31</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="4" t="str">
+      <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E32" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E32" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="str">
+        <v>62.15847756669374</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="5"/>
+        <v>237.84152243330627</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="4"/>
+        <v>13117.062707143943</v>
+      </c>
+      <c r="H32" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6882.937292856057</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A33" s="19">
+        <v>46291</v>
+      </c>
+      <c r="B33" s="24">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="C33" s="20"/>
-      <c r="D33" s="21" t="str">
+      <c r="D33" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E33" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E33" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H33" s="21" t="str">
+        <v>61.051478468650274</v>
+      </c>
+      <c r="F33" s="21">
+        <f t="shared" si="5"/>
+        <v>238.94852153134974</v>
+      </c>
+      <c r="G33" s="21">
+        <f t="shared" si="4"/>
+        <v>12878.114185612594</v>
+      </c>
+      <c r="H33" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>7121.8858143874058</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A34" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B34" s="23">
+        <f t="shared" si="3"/>
+        <v>33</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="4" t="str">
+      <c r="D34" s="4">
         <f t="shared" ref="D34:D65" si="6">IF(AND($A34&lt;&gt;"",$B34&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E34" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F34" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H34" s="4" t="str">
+        <v>59.939327002801001</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="5"/>
+        <v>240.06067299719899</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="4"/>
+        <v>12638.053512615395</v>
+      </c>
+      <c r="H34" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>7361.9464873846046</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A35" s="19">
+        <v>46293</v>
+      </c>
+      <c r="B35" s="24">
+        <f t="shared" si="3"/>
+        <v>34</v>
       </c>
       <c r="C35" s="20"/>
-      <c r="D35" s="21" t="str">
+      <c r="D35" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E35" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E35" s="21">
         <f t="shared" ref="E35:E66" si="7">IF(AND($A35&lt;&gt;"",$B35&lt;&gt;""),G34*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G35" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H35" s="21" t="str">
+        <v>58.821999188192322</v>
+      </c>
+      <c r="F35" s="21">
+        <f t="shared" si="5"/>
+        <v>241.17800081180769</v>
+      </c>
+      <c r="G35" s="21">
+        <f t="shared" si="4"/>
+        <v>12396.875511803588</v>
+      </c>
+      <c r="H35" s="21">
         <f t="shared" ref="H35:H66" si="8">IF(AND($A35&lt;&gt;"",$B35&lt;&gt;""),$K$7-G35,"")</f>
-        <v/>
+        <v>7603.1244881964121</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A36" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B36" s="23">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="4" t="str">
+      <c r="D36" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E36" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E36" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F36" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G36" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H36" s="4" t="str">
+        <v>57.699470932254741</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="5"/>
+        <v>242.30052906774526</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="4"/>
+        <v>12154.574982735843</v>
+      </c>
+      <c r="H36" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>7845.4250172641568</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Thongam_Deme_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Thongam_Deme_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>13500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>12154.574982735843</v>
+        <v>9668.66908863153</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>7845.4250172641568</v>
+        <v>10331.33091136847</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1907,283 +1907,303 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="19"/>
-      <c r="B37" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A37" s="19">
+        <v>46295</v>
+      </c>
+      <c r="B37" s="24">
+        <f t="shared" si="3"/>
+        <v>36</v>
       </c>
       <c r="C37" s="20"/>
-      <c r="D37" s="21" t="str">
+      <c r="D37" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E37" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E37" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F37" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G37" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H37" s="21" t="str">
+        <v>56.571718030283371</v>
+      </c>
+      <c r="F37" s="21">
+        <f t="shared" si="5"/>
+        <v>243.42828196971664</v>
+      </c>
+      <c r="G37" s="21">
+        <f t="shared" si="4"/>
+        <v>11911.146700766127</v>
+      </c>
+      <c r="H37" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>8088.8532992338733</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A38" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B38" s="23">
+        <f t="shared" si="3"/>
+        <v>37</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="4" t="str">
+      <c r="D38" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E38" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E38" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F38" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G38" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H38" s="4" t="str">
+        <v>55.438716164916016</v>
+      </c>
+      <c r="F38" s="4">
+        <f t="shared" si="5"/>
+        <v>244.561283835084</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="4"/>
+        <v>11666.585416931042</v>
+      </c>
+      <c r="H38" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>8333.4145830689577</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
-      <c r="B39" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A39" s="19">
+        <v>46297</v>
+      </c>
+      <c r="B39" s="24">
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="C39" s="20"/>
-      <c r="D39" s="21" t="str">
+      <c r="D39" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E39" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E39" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F39" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G39" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H39" s="21" t="str">
+        <v>54.300440905608809</v>
+      </c>
+      <c r="F39" s="21">
+        <f t="shared" si="5"/>
+        <v>245.69955909439119</v>
+      </c>
+      <c r="G39" s="21">
+        <f t="shared" si="4"/>
+        <v>11420.885857836651</v>
+      </c>
+      <c r="H39" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>8579.1141421633492</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A40" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B40" s="23">
+        <f t="shared" si="3"/>
+        <v>39</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="4" t="str">
+      <c r="D40" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E40" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E40" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F40" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G40" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H40" s="4" t="str">
+        <v>53.156867708109459</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="5"/>
+        <v>246.84313229189053</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="4"/>
+        <v>11174.042725544759</v>
+      </c>
+      <c r="H40" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>8825.9572744552406</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A41" s="19">
+        <v>46299</v>
+      </c>
+      <c r="B41" s="24">
+        <f t="shared" si="3"/>
+        <v>40</v>
       </c>
       <c r="C41" s="20"/>
-      <c r="D41" s="21" t="str">
+      <c r="D41" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E41" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E41" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F41" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G41" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H41" s="21" t="str">
+        <v>52.007971913927967</v>
+      </c>
+      <c r="F41" s="21">
+        <f t="shared" si="5"/>
+        <v>247.99202808607203</v>
+      </c>
+      <c r="G41" s="21">
+        <f t="shared" si="4"/>
+        <v>10926.050697458688</v>
+      </c>
+      <c r="H41" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>9073.9493025413121</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A42" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B42" s="23">
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="4" t="str">
+      <c r="D42" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E42" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E42" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F42" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G42" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H42" s="4" t="str">
+        <v>50.853728749804958</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="5"/>
+        <v>249.14627125019504</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="4"/>
+        <v>10676.904426208494</v>
+      </c>
+      <c r="H42" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>9323.0955737915065</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A43" s="19">
+        <v>46302</v>
+      </c>
+      <c r="B43" s="24">
+        <f t="shared" si="3"/>
+        <v>42</v>
       </c>
       <c r="C43" s="20"/>
-      <c r="D43" s="21" t="str">
+      <c r="D43" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E43" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E43" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F43" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G43" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H43" s="21" t="str">
+        <v>49.69411332717749</v>
+      </c>
+      <c r="F43" s="21">
+        <f t="shared" si="5"/>
+        <v>250.30588667282251</v>
+      </c>
+      <c r="G43" s="21">
+        <f t="shared" si="4"/>
+        <v>10426.598539535671</v>
+      </c>
+      <c r="H43" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>9573.4014604643289</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A44" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B44" s="23">
+        <f t="shared" si="3"/>
+        <v>43</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="4" t="str">
+      <c r="D44" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E44" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E44" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F44" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G44" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H44" s="4" t="str">
+        <v>48.52910064164238</v>
+      </c>
+      <c r="F44" s="4">
+        <f t="shared" si="5"/>
+        <v>251.47089935835763</v>
+      </c>
+      <c r="G44" s="4">
+        <f t="shared" si="4"/>
+        <v>10175.127640177314</v>
+      </c>
+      <c r="H44" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>9824.8723598226861</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A45" s="19">
+        <v>46303</v>
+      </c>
+      <c r="B45" s="24">
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="C45" s="20"/>
-      <c r="D45" s="21" t="str">
+      <c r="D45" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E45" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E45" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F45" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G45" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H45" s="21" t="str">
+        <v>47.35866557241706</v>
+      </c>
+      <c r="F45" s="21">
+        <f t="shared" si="5"/>
+        <v>252.64133442758293</v>
+      </c>
+      <c r="G45" s="21">
+        <f t="shared" si="4"/>
+        <v>9922.4863057497314</v>
+      </c>
+      <c r="H45" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>10077.513694250269</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A46" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B46" s="23">
+        <f t="shared" si="3"/>
+        <v>45</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="4" t="str">
+      <c r="D46" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E46" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E46" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F46" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G46" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H46" s="4" t="str">
+        <v>46.182782881797898</v>
+      </c>
+      <c r="F46" s="4">
+        <f t="shared" si="5"/>
+        <v>253.81721711820211</v>
+      </c>
+      <c r="G46" s="4">
+        <f t="shared" si="4"/>
+        <v>9668.66908863153</v>
+      </c>
+      <c r="H46" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>10331.33091136847</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
